--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2674F32-A8F8-4270-9325-C00CA2A6EAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F8C2CF-78F9-4A3D-9859-A0123FBEADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F8C2CF-78F9-4A3D-9859-A0123FBEADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6D9BE6-978A-4CFF-9EAF-E1E763844EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
@@ -133,6 +133,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -233,54 +236,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,107 +595,107 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="13">
@@ -708,162 +704,162 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="B14" s="14"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="9">
         <v>0.8</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="9">
         <v>0.8</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="11">
         <v>0.15</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="11">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="11">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="13">
@@ -871,7 +867,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="13">
@@ -879,7 +875,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="13">
@@ -887,167 +883,167 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="13"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
+      <c r="A38" s="7"/>
       <c r="B38" s="13"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="9">
         <v>0.8</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="9">
         <v>0.45</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="9">
         <v>0.15</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="9">
         <v>0.05</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="11">
         <v>0.15</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="11">
         <v>0.1</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B58" s="13">
@@ -1055,7 +1051,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="13">
@@ -1063,7 +1059,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B60" s="13">
@@ -1071,163 +1067,163 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+      <c r="A61" s="7"/>
       <c r="B61" s="13"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63" s="9">
         <v>0.8</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="9">
         <v>0.4</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67" s="9">
         <v>0.05</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68" s="9">
         <v>0.05</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69" s="9">
         <v>0.4</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="11">
         <v>0.2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="11">
         <v>0.2</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B81" s="13">
@@ -1235,7 +1231,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B82" s="13">
@@ -1243,7 +1239,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B83" s="13">
@@ -1251,167 +1247,167 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="12"/>
+      <c r="A84" s="7"/>
       <c r="B84" s="13"/>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="12"/>
+      <c r="A85" s="7"/>
       <c r="B85" s="13"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B87" s="5">
+      <c r="B87" s="9">
         <v>0.4</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B88" s="5">
+      <c r="B88" s="9">
         <v>0.4</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B89" s="5">
+      <c r="B89" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B90" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B91" s="9">
         <v>0.05</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B92" s="5">
+      <c r="B92" s="9">
         <v>0.05</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B93" s="5">
+      <c r="B93" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="10">
         <v>0.1</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="11">
         <v>0.2</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="11">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="11">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="11">
         <v>0.05</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B102" s="11">
+      <c r="B102" s="12">
         <v>0.15</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="12">
         <v>0.15</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B104" s="11">
+      <c r="B104" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B105" s="13">
@@ -1419,7 +1415,7 @@
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B106" s="13">
@@ -1427,7 +1423,7 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B107" s="13">
@@ -1435,171 +1431,171 @@
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="12"/>
+      <c r="A108" s="7"/>
       <c r="B108" s="13"/>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B110" s="5">
+      <c r="B110" s="9">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B111" s="5">
+      <c r="B111" s="9">
         <v>0.4</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B112" s="5">
+      <c r="B112" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B113" s="5">
+      <c r="B113" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B114" s="5">
+      <c r="B114" s="9">
         <v>0.05</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B115" s="5">
+      <c r="B115" s="9">
         <v>0.05</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="5">
+      <c r="B116" s="9">
         <v>0.15</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B118" s="14">
+      <c r="B118" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B119" s="14">
+      <c r="B119" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B120" s="9">
+      <c r="B120" s="11">
         <v>0.15</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B121" s="9">
+      <c r="B121" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="8" t="s">
+      <c r="A122" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B123" s="9">
+      <c r="B123" s="11">
         <v>0.15</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="8" t="s">
+      <c r="A124" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="10" t="s">
+      <c r="A125" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B125" s="12">
         <v>0.125</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="10" t="s">
+      <c r="A126" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B126" s="12">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="10" t="s">
+      <c r="A127" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B127" s="11">
+      <c r="B127" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="13">
         <v>0.125</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="12" t="s">
+      <c r="A129" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B129" s="13">
@@ -1607,171 +1603,171 @@
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="12" t="s">
+      <c r="A130" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B130" s="16">
+      <c r="B130" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="12"/>
+      <c r="A131" s="7"/>
       <c r="B131" s="13"/>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B133" s="5">
+      <c r="B133" s="9">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B134" s="5">
+      <c r="B134" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B135" s="5">
+      <c r="B135" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B136" s="5">
+      <c r="B136" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B137" s="5">
+      <c r="B137" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B138" s="5">
+      <c r="B138" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B139" s="5">
+      <c r="B139" s="9">
         <v>0.25</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B141" s="7">
+      <c r="B141" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="6" t="s">
+      <c r="A142" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B143" s="9">
+      <c r="B143" s="11">
         <v>0.2</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="8" t="s">
+      <c r="A144" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B145" s="9">
+      <c r="B145" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="8" t="s">
+      <c r="A146" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B146" s="9">
+      <c r="B146" s="11">
         <v>0.2</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="8" t="s">
+      <c r="A147" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B147" s="9">
+      <c r="B147" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="10" t="s">
+      <c r="A148" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B148" s="11">
+      <c r="B148" s="12">
         <v>0.15</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="10" t="s">
+      <c r="A149" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B150" s="11">
+      <c r="B150" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="12" t="s">
+      <c r="A151" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B151" s="13">
@@ -1779,7 +1775,7 @@
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="12" t="s">
+      <c r="A152" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B152" s="13">
@@ -1787,7 +1783,7 @@
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="12" t="s">
+      <c r="A153" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B153" s="13">
@@ -1795,167 +1791,167 @@
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="12"/>
+      <c r="A154" s="7"/>
       <c r="B154" s="13"/>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
+      <c r="B155" s="14"/>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B157" s="5">
+      <c r="B157" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B158" s="5">
+      <c r="B158" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B159" s="5">
+      <c r="B159" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B160" s="5">
+      <c r="B160" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B161" s="5">
+      <c r="B161" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B162" s="5">
+      <c r="B162" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B163" s="5">
+      <c r="B163" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B164" s="7">
+      <c r="B164" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B165" s="14">
+      <c r="B165" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B166" s="14">
+      <c r="B166" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="8" t="s">
+      <c r="A167" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B167" s="9">
+      <c r="B167" s="11">
         <v>0.15</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" s="8" t="s">
+      <c r="A168" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B168" s="9">
+      <c r="B168" s="11">
         <v>0.05</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="8" t="s">
+      <c r="A169" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B169" s="9">
+      <c r="B169" s="11">
         <v>0.05</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" s="8" t="s">
+      <c r="A170" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B170" s="9">
+      <c r="B170" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="8" t="s">
+      <c r="A171" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B171" s="9">
+      <c r="B171" s="11">
         <v>0.05</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B172" s="11">
+      <c r="B172" s="12">
         <v>0.25</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="10" t="s">
+      <c r="A173" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B173" s="11">
+      <c r="B173" s="12">
         <v>0.25</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" s="10" t="s">
+      <c r="A174" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B174" s="11">
+      <c r="B174" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B175" s="13">
@@ -1963,7 +1959,7 @@
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" s="12" t="s">
+      <c r="A176" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B176" s="13">
@@ -1971,7 +1967,7 @@
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="12" t="s">
+      <c r="A177" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B177" s="13">
@@ -1980,166 +1976,166 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
-      <c r="B178" s="3"/>
+      <c r="B178" s="8"/>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="4"/>
-      <c r="B179" s="5"/>
+      <c r="A179" s="3"/>
+      <c r="B179" s="9"/>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B181" s="5">
+      <c r="B181" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B182" s="5">
+      <c r="B182" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" s="4" t="s">
+      <c r="A183" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B183" s="5">
+      <c r="B183" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" s="4" t="s">
+      <c r="A184" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B184" s="5">
+      <c r="B184" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B185" s="5">
+      <c r="B185" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B186" s="5">
+      <c r="B186" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" s="4" t="s">
+      <c r="A187" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B187" s="5">
+      <c r="B187" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B188" s="7">
+      <c r="B188" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="6" t="s">
+      <c r="A189" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B189" s="14">
+      <c r="B189" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B190" s="14">
+      <c r="B190" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B191" s="9">
+      <c r="B191" s="11">
         <v>0.15</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" s="8" t="s">
+      <c r="A192" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B192" s="9">
+      <c r="B192" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" s="8" t="s">
+      <c r="A193" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B193" s="9">
+      <c r="B193" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" s="8" t="s">
+      <c r="A194" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="11">
         <v>0.15</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" s="8" t="s">
+      <c r="A195" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B195" s="9">
+      <c r="B195" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" s="10" t="s">
+      <c r="A196" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B196" s="11">
+      <c r="B196" s="12">
         <v>0.25</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" s="10" t="s">
+      <c r="A197" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B197" s="11">
+      <c r="B197" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" s="10" t="s">
+      <c r="A198" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B198" s="11">
+      <c r="B198" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" s="12" t="s">
+      <c r="A199" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B199" s="13">
@@ -2147,7 +2143,7 @@
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" s="12" t="s">
+      <c r="A200" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B200" s="13">
@@ -2155,7 +2151,7 @@
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" s="12" t="s">
+      <c r="A201" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B201" s="13">
@@ -2164,166 +2160,166 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
-      <c r="B202" s="3"/>
+      <c r="B202" s="8"/>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" s="4"/>
-      <c r="B203" s="5"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="9"/>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="4" t="s">
+      <c r="A205" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B205" s="5">
+      <c r="B205" s="9">
         <v>0.3</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B206" s="5">
+      <c r="B206" s="9">
         <v>0.2</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" s="4" t="s">
+      <c r="A207" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B207" s="5">
+      <c r="B207" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" s="4" t="s">
+      <c r="A208" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B208" s="5">
+      <c r="B208" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" s="4" t="s">
+      <c r="A209" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B209" s="5">
+      <c r="B209" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" s="4" t="s">
+      <c r="A210" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B210" s="5">
+      <c r="B210" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" s="4" t="s">
+      <c r="A211" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B211" s="5">
+      <c r="B211" s="9">
         <v>0.1</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" s="6" t="s">
+      <c r="A212" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B212" s="7">
+      <c r="B212" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" s="6" t="s">
+      <c r="A213" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B213" s="7">
+      <c r="B213" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B214" s="7">
+      <c r="B214" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" s="8" t="s">
+      <c r="A215" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B215" s="9">
+      <c r="B215" s="11">
         <v>0.2</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" s="8" t="s">
+      <c r="A216" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B216" s="9">
+      <c r="B216" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" s="8" t="s">
+      <c r="A217" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B217" s="9">
+      <c r="B217" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" s="8" t="s">
+      <c r="A218" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B218" s="9">
+      <c r="B218" s="11">
         <v>0.25</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" s="8" t="s">
+      <c r="A219" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B219" s="9">
+      <c r="B219" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" s="10" t="s">
+      <c r="A220" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B220" s="11">
+      <c r="B220" s="12">
         <v>0.3</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" s="10" t="s">
+      <c r="A221" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B221" s="11">
+      <c r="B221" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" s="10" t="s">
+      <c r="A222" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B222" s="11">
+      <c r="B222" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" s="12" t="s">
+      <c r="A223" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B223" s="13">
@@ -2331,7 +2327,7 @@
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" s="12" t="s">
+      <c r="A224" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B224" s="13">
@@ -2339,7 +2335,7 @@
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" s="12" t="s">
+      <c r="A225" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B225" s="13">
@@ -2348,7 +2344,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
-      <c r="B226" s="3"/>
+      <c r="B226" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6D9BE6-978A-4CFF-9EAF-E1E763844EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC6EDA1-0497-4894-B12C-C5BFA7AEF3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -257,26 +257,26 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -591,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3B3171-9700-4F56-9436-A37875560D42}">
-  <dimension ref="A1:B226"/>
+  <dimension ref="A1:B228"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
@@ -1255,24 +1255,20 @@
       <c r="B85" s="13"/>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="7"/>
+      <c r="B86" s="13"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B87" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B87" s="9">
-        <v>0.4</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B88" s="9">
         <v>0.4</v>
@@ -1280,31 +1276,31 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B89" s="9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B91" s="9">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B92" s="9">
         <v>0.05</v>
@@ -1312,55 +1308,55 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B93" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B94" s="10">
-        <v>0.1</v>
+      <c r="B94" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B95" s="10">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B96" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B97" s="11">
-        <v>0.2</v>
+      <c r="B97" s="10">
+        <v>0.05</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B98" s="11">
-        <v>7.4999999999999997E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B99" s="11">
         <v>7.4999999999999997E-2</v>
@@ -1368,31 +1364,31 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B100" s="11">
-        <v>0</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B101" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B102" s="12">
-        <v>0.15</v>
+      <c r="B102" s="11">
+        <v>0.05</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B103" s="12">
         <v>0.15</v>
@@ -1400,951 +1396,963 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B104" s="12">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B104" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B105" s="13">
-        <v>0.15</v>
+      <c r="B105" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B106" s="13">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B107" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B107" s="13">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="7"/>
-      <c r="B108" s="13"/>
+      <c r="B108" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="7"/>
+      <c r="B109" s="13"/>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="7"/>
+      <c r="B110" s="13"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B111" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B110" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B111" s="9">
-        <v>0.4</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B112" s="9">
-        <v>0.2</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B113" s="9">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B114" s="9">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B115" s="9">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B117" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B118" s="9">
         <v>0.15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B117" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" s="10">
-        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B119" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B121" s="10">
         <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B120" s="11">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" s="11">
-        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B122" s="11">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B123" s="11">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B124" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B125" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B124" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B125" s="12">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B126" s="12">
-        <v>7.4999999999999997E-2</v>
+      <c r="B126" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127" s="12">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128" s="12">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B127" s="12">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B128" s="13">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B129" s="13">
+      <c r="B129" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B130" s="13">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B131" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B130" s="13">
+      <c r="B132" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="7"/>
-      <c r="B131" s="13"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="2" t="s">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="7"/>
+      <c r="B133" s="13"/>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B132" s="8" t="s">
+      <c r="B134" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B133" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B134" s="9">
-        <v>0.3</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B135" s="9">
-        <v>0.2</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B136" s="9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B137" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B138" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B139" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B140" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B139" s="9">
+      <c r="B141" s="9">
         <v>0.25</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B140" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" s="10">
-        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B142" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B142" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B143" s="11">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" s="11">
+      <c r="B144" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B145" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B146" s="11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B147" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B148" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B147" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B148" s="12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B149" s="12">
-        <v>0.05</v>
+      <c r="B149" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B150" s="12">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B151" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B150" s="12">
+      <c r="B152" s="12">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B151" s="13">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B152" s="13">
-        <v>0.05</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B153" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B154" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B153" s="13">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
-      <c r="B154" s="13"/>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="1"/>
-      <c r="B155" s="14"/>
+      <c r="B155" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
+      <c r="A156" s="7"/>
+      <c r="B156" s="13"/>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="1"/>
+      <c r="B157" s="14"/>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B158" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B157" s="9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B158" s="9">
-        <v>0.3</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B159" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B160" s="9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B161" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B162" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B163" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B163" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B164" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" s="10">
-        <v>2.5000000000000001E-2</v>
+      <c r="B165" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B166" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B166" s="10">
+      <c r="B168" s="10">
         <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B167" s="11">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" s="11">
-        <v>0.05</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B169" s="11">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B170" s="11">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B171" s="11">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B172" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B171" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B172" s="12">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B173" s="12">
-        <v>0.25</v>
+      <c r="B173" s="11">
+        <v>0.05</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B174" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B175" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B174" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B175" s="13">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B176" s="13">
-        <v>0.1</v>
+      <c r="B176" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B177" s="13">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B178" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B177" s="13">
+      <c r="B179" s="13">
         <v>0.15</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" s="2"/>
-      <c r="B178" s="8"/>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="3"/>
-      <c r="B179" s="9"/>
-    </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
+      <c r="A180" s="2"/>
+      <c r="B180" s="8"/>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="3"/>
+      <c r="B181" s="9"/>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B180" s="8" t="s">
+      <c r="B182" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B181" s="9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B182" s="9">
-        <v>0.3</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B183" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B184" s="9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B185" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B186" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B187" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B188" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B187" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B188" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" s="10">
-        <v>2.5000000000000001E-2</v>
+      <c r="B189" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B190" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B190" s="10">
+      <c r="B192" s="10">
         <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B191" s="11">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" s="11">
-        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B193" s="11">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B194" s="11">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B195" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B196" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B195" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B196" s="12">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B197" s="12">
-        <v>0.05</v>
+      <c r="B197" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B198" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B199" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B198" s="12">
+      <c r="B200" s="12">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B199" s="13">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B200" s="13">
-        <v>0.1</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B201" s="13">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B202" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B201" s="13">
+      <c r="B203" s="13">
         <v>0.15</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" s="2"/>
-      <c r="B202" s="8"/>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" s="3"/>
-      <c r="B203" s="9"/>
-    </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
+      <c r="A204" s="2"/>
+      <c r="B204" s="8"/>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="3"/>
+      <c r="B205" s="9"/>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B204" s="8" t="s">
+      <c r="B206" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B205" s="9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B206" s="9">
-        <v>0.2</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B207" s="9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B208" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B209" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B210" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B211" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B212" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B211" s="9">
+      <c r="B213" s="9">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B212" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B213" s="10">
-        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B214" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B215" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B214" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B215" s="11">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B216" s="11">
+      <c r="B216" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B217" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B218" s="11">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B220" s="11">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B219" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B220" s="12">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B221" s="12">
-        <v>0.1</v>
+      <c r="B221" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222" s="12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B223" s="12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B222" s="12">
+      <c r="B224" s="12">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B223" s="13">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B224" s="13">
-        <v>0.1</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B225" s="13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B226" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B225" s="13">
+      <c r="B227" s="13">
         <v>0.1</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" s="2"/>
-      <c r="B226" s="8"/>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="2"/>
+      <c r="B228" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC6EDA1-0497-4894-B12C-C5BFA7AEF3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AA891D-6393-4518-8177-5C3C444FE600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="33">
   <si>
     <t>ULTRACONSERVADOR</t>
   </si>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>ARROJADO RENDA USUFRUTO</t>
+  </si>
+  <si>
+    <t>Bancário Pré</t>
+  </si>
+  <si>
+    <t>Tesouro Pré</t>
   </si>
 </sst>
 </file>
@@ -780,7 +786,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B24" s="10">
         <v>2.5000000000000001E-2</v>
@@ -788,7 +794,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B25" s="10">
         <v>2.5000000000000001E-2</v>
@@ -964,7 +970,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B48" s="10">
         <v>2.5000000000000001E-2</v>
@@ -972,7 +978,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B49" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1144,7 +1150,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B71" s="10">
         <v>0</v>
@@ -1152,7 +1158,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B72" s="10">
         <v>0</v>
@@ -1332,7 +1338,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B96" s="10">
         <v>0.05</v>
@@ -1340,7 +1346,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B97" s="10">
         <v>0.05</v>
@@ -1516,7 +1522,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B120" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1524,7 +1530,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B121" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1696,7 +1702,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B143" s="10">
         <v>0</v>
@@ -1704,7 +1710,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B144" s="10">
         <v>0</v>
@@ -1880,7 +1886,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B167" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1888,7 +1894,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B168" s="10">
         <v>2.5000000000000001E-2</v>
@@ -2064,7 +2070,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B191" s="10">
         <v>2.5000000000000001E-2</v>
@@ -2072,7 +2078,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B192" s="10">
         <v>2.5000000000000001E-2</v>
@@ -2248,7 +2254,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B215" s="10">
         <v>0</v>
@@ -2256,7 +2262,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B216" s="10">
         <v>0</v>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AA891D-6393-4518-8177-5C3C444FE600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBAD317-7D53-4315-ACD7-6CB61AF872BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -597,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3B3171-9700-4F56-9436-A37875560D42}">
-  <dimension ref="A1:B228"/>
+  <dimension ref="A1:B229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
@@ -1629,56 +1629,52 @@
       <c r="B133" s="13"/>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="7"/>
+      <c r="B134" s="13"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B135" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B135" s="9">
-        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B136" s="9">
-        <v>0.3</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B137" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B138" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B139" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B140" s="9">
         <v>0</v>
@@ -1686,23 +1682,23 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B141" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B141" s="9">
+      <c r="B142" s="9">
         <v>0.25</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B142" s="10">
-        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B143" s="10">
         <v>0</v>
@@ -1710,31 +1706,31 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B144" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B144" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B145" s="11">
-        <v>0.2</v>
+      <c r="B145" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B146" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B147" s="11">
         <v>0</v>
@@ -1742,95 +1738,95 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B148" s="11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B149" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B149" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B150" s="12">
-        <v>0.15</v>
+      <c r="B150" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B151" s="12">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B152" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B152" s="12">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B153" s="13">
+      <c r="B153" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B154" s="13">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B155" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B155" s="13">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
-      <c r="B156" s="13"/>
+      <c r="B156" s="13">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
-      <c r="B157" s="14"/>
+      <c r="A157" s="7"/>
+      <c r="B157" s="13"/>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="2" t="s">
+      <c r="A158" s="1"/>
+      <c r="B158" s="14"/>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="B159" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B159" s="9">
-        <v>0.3</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B160" s="9">
         <v>0.3</v>
@@ -1838,31 +1834,31 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B161" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B162" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B163" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B164" s="9">
         <v>0</v>
@@ -1870,55 +1866,55 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B165" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B166" s="10">
-        <v>0.05</v>
+      <c r="B166" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B167" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B168" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B169" s="11">
-        <v>0.15</v>
+      <c r="A169" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B169" s="10">
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B170" s="11">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B171" s="11">
         <v>0.05</v>
@@ -1926,31 +1922,31 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B172" s="11">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B173" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B173" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B174" s="12">
-        <v>0.25</v>
+      <c r="B174" s="11">
+        <v>0.05</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B175" s="12">
         <v>0.25</v>
@@ -1958,63 +1954,63 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B176" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B176" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B177" s="13">
-        <v>0.25</v>
+      <c r="B177" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B178" s="13">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B179" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B179" s="13">
+      <c r="B180" s="13">
         <v>0.15</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" s="2"/>
-      <c r="B180" s="8"/>
-    </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="3"/>
-      <c r="B181" s="9"/>
+      <c r="A181" s="2"/>
+      <c r="B181" s="8"/>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
+      <c r="A182" s="3"/>
+      <c r="B182" s="9"/>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B182" s="8" t="s">
+      <c r="B183" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B183" s="9">
-        <v>0.3</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B184" s="9">
         <v>0.3</v>
@@ -2022,31 +2018,31 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B185" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B186" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B187" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B188" s="9">
         <v>0</v>
@@ -2054,55 +2050,55 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B189" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B189" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B190" s="10">
-        <v>0.05</v>
+      <c r="B190" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B191" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B192" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B193" s="11">
-        <v>0.15</v>
+      <c r="A193" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B193" s="10">
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B194" s="11">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B195" s="11">
         <v>0</v>
@@ -2110,111 +2106,111 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B196" s="11">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B197" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B197" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B198" s="12">
-        <v>0.25</v>
+      <c r="B198" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B199" s="12">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B200" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B200" s="12">
+      <c r="B201" s="12">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B201" s="13">
-        <v>0.25</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B202" s="13">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B203" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B203" s="13">
+      <c r="B204" s="13">
         <v>0.15</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="8"/>
-    </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="3"/>
-      <c r="B205" s="9"/>
+      <c r="A205" s="2"/>
+      <c r="B205" s="8"/>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="2" t="s">
+      <c r="A206" s="3"/>
+      <c r="B206" s="9"/>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B206" s="8" t="s">
+      <c r="B207" s="8" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B207" s="9">
-        <v>0.3</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B208" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B209" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B210" s="9">
         <v>0.1</v>
@@ -2222,15 +2218,15 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B211" s="9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B212" s="9">
         <v>0</v>
@@ -2238,23 +2234,23 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B213" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B213" s="9">
+      <c r="B214" s="9">
         <v>0.1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B214" s="10">
-        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B215" s="10">
         <v>0</v>
@@ -2262,31 +2258,31 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B216" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B216" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B217" s="11">
-        <v>0.2</v>
+      <c r="B217" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B218" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B219" s="11">
         <v>0</v>
@@ -2294,71 +2290,79 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B220" s="11">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B221" s="11">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B221" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B222" s="12">
-        <v>0.3</v>
+      <c r="B222" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B223" s="12">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B224" s="12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B224" s="12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B225" s="13">
+      <c r="B225" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B226" s="13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B227" s="13">
         <v>0.1</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" s="2"/>
-      <c r="B228" s="8"/>
+      <c r="A228" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B228" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="2"/>
+      <c r="B229" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBAD317-7D53-4315-ACD7-6CB61AF872BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B47B46-D4E5-47CC-A193-5CD1E9A56733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="33">
   <si>
-    <t>ULTRACONSERVADOR</t>
-  </si>
-  <si>
     <t>Neutro</t>
   </si>
   <si>
@@ -78,9 +75,6 @@
     <t xml:space="preserve">Internacional </t>
   </si>
   <si>
-    <t>CONSERVADOR</t>
-  </si>
-  <si>
     <t>Bancário</t>
   </si>
   <si>
@@ -105,34 +99,40 @@
     <t>Renda Variável</t>
   </si>
   <si>
-    <t>CONSERVADOR RENDA CONSTRUÇÃO</t>
-  </si>
-  <si>
-    <t>CONSERVADOR RENDA USUFRUTO</t>
-  </si>
-  <si>
-    <t>MODERADO</t>
-  </si>
-  <si>
-    <t>MODERADO RENDA CONSTRUÇÃO</t>
-  </si>
-  <si>
-    <t>MODERADO RENDA USUFRUTO</t>
-  </si>
-  <si>
-    <t>ARROJADO</t>
-  </si>
-  <si>
-    <t>ARROJADO RENDA CONSTRUÇÃO</t>
-  </si>
-  <si>
-    <t>ARROJADO RENDA USUFRUTO</t>
-  </si>
-  <si>
     <t>Bancário Pré</t>
   </si>
   <si>
     <t>Tesouro Pré</t>
+  </si>
+  <si>
+    <t>Ultraconservador</t>
+  </si>
+  <si>
+    <t>Conservador</t>
+  </si>
+  <si>
+    <t>Conservador Renda Construção</t>
+  </si>
+  <si>
+    <t>Conservador Renda Usufruto</t>
+  </si>
+  <si>
+    <t>Moderado</t>
+  </si>
+  <si>
+    <t>Moderado Renda Construção</t>
+  </si>
+  <si>
+    <t>Moderado Renda Usufruto</t>
+  </si>
+  <si>
+    <t>Arrojado</t>
+  </si>
+  <si>
+    <t>Arrojado Renda Construção</t>
+  </si>
+  <si>
+    <t>Arrojado Renda Usufruto</t>
   </si>
 </sst>
 </file>
@@ -606,15 +606,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="9">
         <v>1</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="9">
         <v>1</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="9">
         <v>0.3</v>
@@ -638,7 +638,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9">
         <v>0.3</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="9">
         <v>0.2</v>
@@ -654,7 +654,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9">
         <v>0.1</v>
@@ -662,7 +662,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="9">
         <v>0.1</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9">
         <v>0</v>
@@ -678,7 +678,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="10">
         <v>0</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="11">
         <v>0</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="12">
         <v>0</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="13">
         <v>0</v>
@@ -714,15 +714,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="9">
         <v>0.8</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="9">
         <v>0.8</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="9">
         <v>0.2</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="9">
         <v>0.2</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="9">
         <v>0.2</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="9">
         <v>0.2</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="9">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" s="10">
         <v>0.05</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B24" s="10">
         <v>2.5000000000000001E-2</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B25" s="10">
         <v>2.5000000000000001E-2</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="11">
         <v>0.15</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B27" s="11">
         <v>7.4999999999999997E-2</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B28" s="11">
         <v>7.4999999999999997E-2</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B29" s="11">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B30" s="11">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="12">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B32" s="12">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B33" s="12">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" s="13">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B35" s="13">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B36" s="13">
         <v>0</v>
@@ -898,15 +898,15 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" s="9">
         <v>0.8</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" s="9">
         <v>0.45</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="9">
         <v>0.2</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" s="9">
         <v>0.15</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B44" s="9">
         <v>0.1</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B45" s="9">
         <v>0.05</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46" s="9">
         <v>0.3</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B47" s="10">
         <v>0.05</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B48" s="10">
         <v>2.5000000000000001E-2</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B49" s="10">
         <v>2.5000000000000001E-2</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B50" s="11">
         <v>0.15</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B51" s="11">
         <v>2.5000000000000001E-2</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B52" s="11">
         <v>2.5000000000000001E-2</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B53" s="11">
         <v>0.1</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B54" s="11">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" s="12">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B56" s="12">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B57" s="12">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" s="13">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B59" s="13">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B60" s="13">
         <v>0</v>
@@ -1078,15 +1078,15 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B63" s="9">
         <v>0.8</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B64" s="9">
         <v>0.4</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B65" s="9">
         <v>0.2</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B66" s="9">
         <v>0.1</v>
@@ -1118,7 +1118,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B67" s="9">
         <v>0.05</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B68" s="9">
         <v>0.05</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B69" s="9">
         <v>0.4</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B70" s="10">
         <v>0</v>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B71" s="10">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B72" s="10">
         <v>0</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" s="11">
         <v>0.2</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B74" s="11">
         <v>0</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B75" s="11">
         <v>0</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B76" s="11">
         <v>0.2</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B77" s="11">
         <v>0</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" s="12">
         <v>0</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B79" s="12">
         <v>0</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B80" s="12">
         <v>0</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B81" s="13">
         <v>0</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B82" s="13">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B83" s="13">
         <v>0</v>
@@ -1266,15 +1266,15 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B88" s="9">
         <v>0.4</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B89" s="9">
         <v>0.4</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B90" s="9">
         <v>0.2</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" s="9">
         <v>0.1</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B92" s="9">
         <v>0.05</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B93" s="9">
         <v>0.05</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B94" s="9">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B95" s="10">
         <v>0.1</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B96" s="10">
         <v>0.05</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B97" s="10">
         <v>0.05</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B98" s="11">
         <v>0.2</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B99" s="11">
         <v>7.4999999999999997E-2</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B100" s="11">
         <v>7.4999999999999997E-2</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B101" s="11">
         <v>0</v>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B102" s="11">
         <v>0.05</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B103" s="12">
         <v>0.15</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B104" s="12">
         <v>0.15</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B105" s="12">
         <v>0</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B106" s="13">
         <v>0.15</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B107" s="13">
         <v>0.05</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B108" s="13">
         <v>0.05</v>
@@ -1450,15 +1450,15 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B112" s="9">
         <v>0.55000000000000004</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B113" s="9">
         <v>0.4</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B114" s="9">
         <v>0.2</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B115" s="9">
         <v>0.1</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B116" s="9">
         <v>0.05</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B117" s="9">
         <v>0.05</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B118" s="9">
         <v>0.15</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B119" s="10">
         <v>0.05</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B120" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B121" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B122" s="11">
         <v>0.15</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B123" s="11">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B124" s="11">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B125" s="11">
         <v>0.15</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B126" s="11">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B127" s="12">
         <v>0.125</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B128" s="12">
         <v>7.4999999999999997E-2</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B129" s="12">
         <v>0.05</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B130" s="13">
         <v>0.125</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B131" s="13">
         <v>0.05</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B132" s="13">
         <v>7.4999999999999997E-2</v>
@@ -1634,15 +1634,15 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B136" s="9">
         <v>0.55000000000000004</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B137" s="9">
         <v>0.3</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B138" s="9">
         <v>0.2</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B139" s="9">
         <v>0.1</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B140" s="9">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B141" s="9">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B142" s="9">
         <v>0.25</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B143" s="10">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B144" s="10">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B145" s="10">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B146" s="11">
         <v>0.2</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B147" s="11">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B148" s="11">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B149" s="11">
         <v>0.2</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B150" s="11">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151" s="12">
         <v>0.15</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B152" s="12">
         <v>0.05</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B153" s="12">
         <v>0.1</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B154" s="13">
         <v>0.1</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B155" s="13">
         <v>0.05</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B156" s="13">
         <v>0.05</v>
@@ -1818,15 +1818,15 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B160" s="9">
         <v>0.3</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B161" s="9">
         <v>0.3</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B162" s="9">
         <v>0.2</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B163" s="9">
         <v>0.1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B164" s="9">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B165" s="9">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B166" s="9">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B167" s="10">
         <v>0.05</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B168" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B169" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B170" s="11">
         <v>0.15</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B171" s="11">
         <v>0.05</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B172" s="11">
         <v>0.05</v>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B173" s="11">
         <v>0</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B174" s="11">
         <v>0.05</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B175" s="12">
         <v>0.25</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B176" s="12">
         <v>0.25</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B177" s="12">
         <v>0</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B178" s="13">
         <v>0.25</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B179" s="13">
         <v>0.1</v>
@@ -1986,7 +1986,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B180" s="13">
         <v>0.15</v>
@@ -2002,15 +2002,15 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B184" s="9">
         <v>0.3</v>
@@ -2018,7 +2018,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B185" s="9">
         <v>0.3</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B186" s="9">
         <v>0.2</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B187" s="9">
         <v>0.1</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B188" s="9">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B189" s="9">
         <v>0</v>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B190" s="9">
         <v>0</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B191" s="10">
         <v>0.05</v>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B192" s="10">
         <v>2.5000000000000001E-2</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B193" s="10">
         <v>2.5000000000000001E-2</v>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B194" s="11">
         <v>0.15</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B195" s="11">
         <v>0</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B196" s="11">
         <v>0</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B197" s="11">
         <v>0.15</v>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B198" s="11">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B199" s="12">
         <v>0.25</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B200" s="12">
         <v>0.05</v>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B201" s="12">
         <v>0.2</v>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B202" s="13">
         <v>0.25</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B203" s="13">
         <v>0.1</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B204" s="13">
         <v>0.15</v>
@@ -2186,15 +2186,15 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B208" s="9">
         <v>0.3</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B209" s="9">
         <v>0.2</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B210" s="9">
         <v>0.1</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B211" s="9">
         <v>0.1</v>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B212" s="9">
         <v>0</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B213" s="9">
         <v>0</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B214" s="9">
         <v>0.1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B215" s="10">
         <v>0</v>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B216" s="10">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B217" s="10">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B218" s="11">
         <v>0.2</v>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B219" s="11">
         <v>0</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B220" s="11">
         <v>0</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B221" s="11">
         <v>0.25</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B222" s="11">
         <v>0</v>
@@ -2314,7 +2314,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B223" s="12">
         <v>0.3</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B224" s="12">
         <v>0.1</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B225" s="12">
         <v>0.2</v>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B226" s="13">
         <v>0.2</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B227" s="13">
         <v>0.1</v>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B228" s="13">
         <v>0.1</v>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B47B46-D4E5-47CC-A193-5CD1E9A56733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C9E227-EF0C-4365-956B-B0898D99BDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -909,7 +900,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="9">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -917,7 +908,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="9">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -957,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="9">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -965,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="10">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -973,7 +964,7 @@
         <v>21</v>
       </c>
       <c r="B48" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -981,7 +972,7 @@
         <v>22</v>
       </c>
       <c r="B49" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -989,7 +980,7 @@
         <v>10</v>
       </c>
       <c r="B50" s="11">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -997,7 +988,7 @@
         <v>13</v>
       </c>
       <c r="B51" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1005,7 +996,7 @@
         <v>14</v>
       </c>
       <c r="B52" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1549,7 +1540,7 @@
         <v>13</v>
       </c>
       <c r="B123" s="11">
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -1557,7 +1548,7 @@
         <v>14</v>
       </c>
       <c r="B124" s="11">
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -1565,7 +1556,7 @@
         <v>15</v>
       </c>
       <c r="B125" s="11">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -2013,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="B184" s="9">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -2061,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="B190" s="9">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -2101,7 +2092,7 @@
         <v>13</v>
       </c>
       <c r="B195" s="11">
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -2109,7 +2100,7 @@
         <v>14</v>
       </c>
       <c r="B196" s="11">
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -2117,7 +2108,7 @@
         <v>15</v>
       </c>
       <c r="B197" s="11">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -2133,7 +2124,7 @@
         <v>11</v>
       </c>
       <c r="B199" s="12">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -2149,7 +2140,7 @@
         <v>18</v>
       </c>
       <c r="B201" s="12">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -2301,7 +2292,7 @@
         <v>15</v>
       </c>
       <c r="B221" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C9E227-EF0C-4365-956B-B0898D99BDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4690974-31A0-4EDA-8792-BCA87A7D5923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
+    <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="34">
   <si>
     <t>Neutro</t>
   </si>
@@ -108,9 +108,6 @@
     <t>Conservador Renda Usufruto</t>
   </si>
   <si>
-    <t>Moderado</t>
-  </si>
-  <si>
     <t>Moderado Renda Construção</t>
   </si>
   <si>
@@ -124,6 +121,12 @@
   </si>
   <si>
     <t>Arrojado Renda Usufruto</t>
+  </si>
+  <si>
+    <t>MODERADO RENDA CONSTRUÇÃO</t>
+  </si>
+  <si>
+    <t>Ações Qualidade</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1260,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>0</v>
@@ -1268,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="B88" s="9">
-        <v>0.4</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1316,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="B94" s="9">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -1324,23 +1327,23 @@
         <v>9</v>
       </c>
       <c r="B95" s="10">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B96" s="10">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B97" s="10">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -1348,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -1356,7 +1359,7 @@
         <v>13</v>
       </c>
       <c r="B99" s="11">
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -1364,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="B100" s="11">
-        <v>7.4999999999999997E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -1372,7 +1375,7 @@
         <v>15</v>
       </c>
       <c r="B101" s="11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -1380,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="B102" s="11">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -1388,15 +1391,15 @@
         <v>11</v>
       </c>
       <c r="B103" s="12">
-        <v>0.15</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B104" s="12">
-        <v>0.15</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -1404,7 +1407,7 @@
         <v>18</v>
       </c>
       <c r="B105" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -1412,7 +1415,7 @@
         <v>12</v>
       </c>
       <c r="B106" s="13">
-        <v>0.15</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -1428,7 +1431,7 @@
         <v>20</v>
       </c>
       <c r="B108" s="13">
-        <v>0.05</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -1441,7 +1444,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B111" s="8" t="s">
         <v>0</v>
@@ -1625,7 +1628,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>0</v>
@@ -1809,7 +1812,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B159" s="8" t="s">
         <v>0</v>
@@ -1993,7 +1996,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>0</v>
@@ -2177,7 +2180,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>0</v>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4690974-31A0-4EDA-8792-BCA87A7D5923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A300C83-0EB3-4858-9F5A-34DCF89D71BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
@@ -123,10 +123,10 @@
     <t>Arrojado Renda Usufruto</t>
   </si>
   <si>
-    <t>MODERADO RENDA CONSTRUÇÃO</t>
-  </si>
-  <si>
     <t>Ações Qualidade</t>
+  </si>
+  <si>
+    <t>Moderado</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="B88" s="9">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1319,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="B94" s="9">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -1327,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="B95" s="10">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -1335,7 +1335,7 @@
         <v>13</v>
       </c>
       <c r="B96" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -1343,7 +1343,7 @@
         <v>14</v>
       </c>
       <c r="B97" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -1351,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -1359,7 +1359,7 @@
         <v>13</v>
       </c>
       <c r="B99" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -1367,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="B100" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -1375,7 +1375,7 @@
         <v>15</v>
       </c>
       <c r="B101" s="11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -1391,15 +1391,15 @@
         <v>11</v>
       </c>
       <c r="B103" s="12">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B104" s="12">
-        <v>7.4999999999999997E-2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -1407,7 +1407,7 @@
         <v>18</v>
       </c>
       <c r="B105" s="12">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -1415,7 +1415,7 @@
         <v>12</v>
       </c>
       <c r="B106" s="13">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -1423,7 +1423,7 @@
         <v>19</v>
       </c>
       <c r="B107" s="13">
-        <v>0.05</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos\Aplicativo Alocação\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A300C83-0EB3-4858-9F5A-34DCF89D71BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A8FA99-3D47-4978-95A3-EE018867B800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="36">
   <si>
     <t>Neutro</t>
   </si>
@@ -42,15 +42,9 @@
     <t>1 a 30 dias</t>
   </si>
   <si>
-    <t>31 a 180 dias</t>
-  </si>
-  <si>
     <t>181 a 360 dias</t>
   </si>
   <si>
-    <t>361+ dias</t>
-  </si>
-  <si>
     <t>FiInfra e Cetipados</t>
   </si>
   <si>
@@ -78,9 +72,6 @@
     <t>Crédito Privado</t>
   </si>
   <si>
-    <t>Ações</t>
-  </si>
-  <si>
     <t>FIIs</t>
   </si>
   <si>
@@ -90,43 +81,58 @@
     <t>Renda Variável</t>
   </si>
   <si>
-    <t>Bancário Pré</t>
-  </si>
-  <si>
-    <t>Tesouro Pré</t>
-  </si>
-  <si>
-    <t>Ultraconservador</t>
-  </si>
-  <si>
-    <t>Conservador</t>
-  </si>
-  <si>
-    <t>Conservador Renda Construção</t>
-  </si>
-  <si>
-    <t>Conservador Renda Usufruto</t>
-  </si>
-  <si>
-    <t>Moderado Renda Construção</t>
-  </si>
-  <si>
-    <t>Moderado Renda Usufruto</t>
-  </si>
-  <si>
-    <t>Arrojado</t>
-  </si>
-  <si>
-    <t>Arrojado Renda Construção</t>
-  </si>
-  <si>
-    <t>Arrojado Renda Usufruto</t>
-  </si>
-  <si>
     <t>Ações Qualidade</t>
   </si>
   <si>
-    <t>Moderado</t>
+    <t>ULTRACONSERVADOR</t>
+  </si>
+  <si>
+    <t>Mín</t>
+  </si>
+  <si>
+    <t>31 a 90 dias</t>
+  </si>
+  <si>
+    <t>91 a 180 dias</t>
+  </si>
+  <si>
+    <t>CONSERVADOR</t>
+  </si>
+  <si>
+    <t>CONSERVADOR RENDA CONSTRUÇÃO</t>
+  </si>
+  <si>
+    <t>CONSERVADOR RENDA USUFRUTO</t>
+  </si>
+  <si>
+    <t>Ações Renda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSERVADOR INTERNACIONAL </t>
+  </si>
+  <si>
+    <t>CONSERVADOR INT. RENDA CONSTRUÇÃO</t>
+  </si>
+  <si>
+    <t>CONSERVADOR INT. RENDA USUFRUTO</t>
+  </si>
+  <si>
+    <t>MODERADO</t>
+  </si>
+  <si>
+    <t>MODERADO RENDA CONSTRUÇÃO</t>
+  </si>
+  <si>
+    <t>MODERADO RENDA USUFRUTO</t>
+  </si>
+  <si>
+    <t>ARROJADO</t>
+  </si>
+  <si>
+    <t>ARROJADO RENDA CONSTRUÇÃO</t>
+  </si>
+  <si>
+    <t>ARROJADO RENDA USUFRUTO</t>
   </si>
 </sst>
 </file>
@@ -236,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -277,6 +283,15 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -591,130 +606,154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3B3171-9700-4F56-9436-A37875560D42}">
-  <dimension ref="A1:B229"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.140625" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="9">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="9">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B8" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B11" s="11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="12">
+        <v>0</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="B13" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="14"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>1</v>
       </c>
@@ -748,7 +787,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B20" s="9">
         <v>0.2</v>
@@ -756,39 +795,39 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B21" s="9">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B22" s="9">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B23" s="10">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B24" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B25" s="10">
         <v>2.5000000000000001E-2</v>
@@ -796,23 +835,23 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B26" s="11">
-        <v>0.15</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B27" s="11">
-        <v>7.4999999999999997E-2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B28" s="11">
         <v>7.4999999999999997E-2</v>
@@ -820,15 +859,15 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B29" s="11">
-        <v>0</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B30" s="11">
         <v>0</v>
@@ -836,7 +875,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B31" s="12">
         <v>0</v>
@@ -844,13 +883,13 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B32" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>18</v>
       </c>
@@ -858,47 +897,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B34" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B35" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B36" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="13"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="13"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="18"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>1</v>
       </c>
@@ -906,7 +951,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>2</v>
       </c>
@@ -914,7 +959,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,7 +967,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>4</v>
       </c>
@@ -930,111 +975,111 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B44" s="9">
         <v>0.1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B45" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B46" s="9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B47" s="10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="10">
         <v>0.1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B49" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B50" s="11">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B51" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B52" s="11">
         <v>0.05</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B53" s="11">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="11">
         <v>0.1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B54" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B55" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B56" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>18</v>
       </c>
@@ -1042,85 +1087,86 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B58" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B59" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B60" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
-      <c r="B61" s="13"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="18"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="20"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B64" s="9">
         <v>0.8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B64" s="9">
-        <v>0.4</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B65" s="9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B66" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67" s="9">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B68" s="9">
         <v>0.05</v>
@@ -1128,47 +1174,47 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B69" s="9">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70" s="10">
+      <c r="A70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B71" s="10">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B72" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B73" s="11">
-        <v>0.2</v>
+      <c r="A73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B74" s="11">
         <v>0</v>
@@ -1176,39 +1222,39 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B75" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B76" s="11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B77" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" s="12">
-        <v>0</v>
+      <c r="A78" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" s="11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B79" s="12">
         <v>0</v>
@@ -1216,73 +1262,82 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B80" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B81" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B82" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B83" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
-      <c r="B84" s="13"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="7"/>
-      <c r="B85" s="13"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="7"/>
-      <c r="B86" s="13"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B85" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="18"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="20"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B88" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B89" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,119 +1345,119 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B91" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B92" s="9">
         <v>0.1</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B92" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B93" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B94" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B95" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B96" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" s="11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B97" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B98" s="11">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B99" s="11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B100" s="11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B102" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="B103" s="12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B104" s="12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>18</v>
       </c>
@@ -1410,52 +1465,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B106" s="13">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B107" s="13">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B108" s="13">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
-      <c r="B109" s="13"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="7"/>
-      <c r="B110" s="13"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B109" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="18"/>
+      <c r="B110" s="19"/>
+      <c r="C110" s="20"/>
+      <c r="D110" s="20"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B111" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B112" s="9">
-        <v>0.55000000000000004</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -1463,7 +1524,7 @@
         <v>2</v>
       </c>
       <c r="B113" s="9">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -1484,7 +1545,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B116" s="9">
         <v>0.05</v>
@@ -1492,39 +1553,39 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B117" s="9">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B118" s="9">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B119" s="10">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B120" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B121" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1532,125 +1593,130 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B122" s="11">
-        <v>0.15</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B123" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B124" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B125" s="11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B126" s="11">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B127" s="12">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B128" s="12">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B129" s="12">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B130" s="13">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B131" s="13">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B132" s="13">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="7"/>
-      <c r="B133" s="13"/>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
-      <c r="B134" s="13"/>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B133" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="18"/>
+      <c r="B134" s="19"/>
+      <c r="C134" s="20"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B136" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B137" s="9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,172 +1724,178 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B139" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B140" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B141" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B140" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
+      <c r="B142" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B141" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
+      <c r="B143" s="10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B144" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B142" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
+      <c r="B147" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B148" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B149" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B150" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B151" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B143" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B144" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B145" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
+      <c r="B152" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B153" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B146" s="11">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B147" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B148" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" s="11">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
+      <c r="B155" s="13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B150" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B151" s="12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="6" t="s">
+      <c r="B156" s="13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B152" s="12">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B153" s="12">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B154" s="13">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B155" s="13">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B156" s="13">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
-      <c r="B157" s="13"/>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="1"/>
-      <c r="B158" s="14"/>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="18"/>
+      <c r="B158" s="19"/>
+      <c r="C158" s="20"/>
+      <c r="D158" s="20"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B159" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B160" s="9">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -1831,7 +1903,7 @@
         <v>2</v>
       </c>
       <c r="B161" s="9">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -1852,23 +1924,23 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B164" s="9">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B165" s="9">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B166" s="9">
         <v>0</v>
@@ -1876,149 +1948,158 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B167" s="10">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B168" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B169" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B170" s="11">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B171" s="11">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B172" s="11">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B173" s="11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B174" s="11">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B175" s="12">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B176" s="12">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B177" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B178" s="13">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B179" s="13">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B180" s="13">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="2"/>
-      <c r="B181" s="8"/>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="3"/>
-      <c r="B182" s="9"/>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B181" s="13">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="18"/>
+      <c r="B182" s="19"/>
+      <c r="C182" s="20"/>
+      <c r="D182" s="20"/>
+      <c r="E182" s="20"/>
+      <c r="F182" s="20"/>
+      <c r="G182" s="20"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B184" s="9">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B185" s="9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>3</v>
       </c>
@@ -2026,7 +2107,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>4</v>
       </c>
@@ -2034,164 +2115,170 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B188" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B189" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B188" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="3" t="s">
+      <c r="B190" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B189" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B190" s="9">
+      <c r="B191" s="10">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B192" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B191" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B192" s="10">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B193" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B194" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195" s="11">
         <v>0.15</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B195" s="11">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B196" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B197" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B198" s="11">
         <v>0.1</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B198" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B199" s="12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B200" s="12">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B201" s="12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B202" s="13">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B203" s="13">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B204" s="13">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="8"/>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" s="3"/>
-      <c r="B206" s="9"/>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B205" s="13">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="18"/>
+      <c r="B206" s="19"/>
+      <c r="C206" s="20"/>
+      <c r="D206" s="20"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B208" s="9">
-        <v>0.3</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -2199,7 +2286,7 @@
         <v>2</v>
       </c>
       <c r="B209" s="9">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -2207,7 +2294,7 @@
         <v>3</v>
       </c>
       <c r="B210" s="9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -2220,7 +2307,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B212" s="9">
         <v>0</v>
@@ -2228,7 +2315,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B213" s="9">
         <v>0</v>
@@ -2236,23 +2323,23 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B214" s="9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B215" s="10">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B216" s="10">
         <v>0</v>
@@ -2260,7 +2347,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B217" s="10">
         <v>0</v>
@@ -2268,23 +2355,23 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B218" s="11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B219" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B220" s="11">
         <v>0</v>
@@ -2292,55 +2379,55 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B221" s="11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B222" s="11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B223" s="12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B224" s="12">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B225" s="12">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B226" s="13">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B227" s="13">
         <v>0.1</v>
@@ -2348,15 +2435,583 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B228" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B229" s="13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="1"/>
+      <c r="B230" s="14"/>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B232" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B233" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B234" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B235" s="9">
         <v>0.1</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" s="2"/>
-      <c r="B229" s="8"/>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B236" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B237" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B238" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B239" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B240" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B241" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B243" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B244" s="11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B245" s="11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B246" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B247" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B248" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B249" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B250" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B251" s="13">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B253" s="13">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="3"/>
+      <c r="B254" s="9"/>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B256" s="9">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B257" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B258" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B259" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B260" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B261" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B262" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B263" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B264" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B265" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B266" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B267" s="11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B268" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B269" s="11">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B270" s="11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B271" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B272" s="12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B273" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B274" s="13">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B275" s="13">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B276" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B277" s="13">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="3"/>
+      <c r="B278" s="9"/>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B280" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B281" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B282" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B283" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B284" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B285" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B286" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B287" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B288" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B289" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B291" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B292" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B293" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B294" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B295" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B296" s="12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B297" s="12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B298" s="13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B299" s="13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B300" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B301" s="13">
+        <v>0.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Pesos-alocacao.xlsx
+++ b/Pesos-alocacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Aplicativo Alocação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A8FA99-3D47-4978-95A3-EE018867B800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C119194E-C213-40A1-BBCB-48A257202640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6588D233-725A-4278-A2B2-1936B18D6634}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="35">
   <si>
     <t>Neutro</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Renda Variável</t>
   </si>
   <si>
-    <t>Ações Qualidade</t>
-  </si>
-  <si>
     <t>ULTRACONSERVADOR</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>CONSERVADOR RENDA USUFRUTO</t>
   </si>
   <si>
-    <t>Ações Renda</t>
-  </si>
-  <si>
     <t xml:space="preserve">CONSERVADOR INTERNACIONAL </t>
   </si>
   <si>
@@ -133,6 +127,9 @@
   </si>
   <si>
     <t>ARROJADO RENDA USUFRUTO</t>
+  </si>
+  <si>
+    <t>Ações</t>
   </si>
 </sst>
 </file>
@@ -242,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -285,13 +282,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3B3171-9700-4F56-9436-A37875560D42}">
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
@@ -615,10 +611,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -663,7 +659,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="9">
         <v>0.2</v>
@@ -673,7 +669,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="9">
         <v>0.15</v>
@@ -747,7 +743,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>0</v>
@@ -787,7 +783,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="9">
         <v>0.2</v>
@@ -795,7 +791,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="9">
         <v>0.15</v>
@@ -889,15 +885,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B33" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>15</v>
       </c>
@@ -905,7 +901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>10</v>
       </c>
@@ -913,7 +909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>16</v>
       </c>
@@ -921,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>17</v>
       </c>
@@ -929,21 +925,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="18"/>
       <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>1</v>
       </c>
@@ -951,7 +945,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>2</v>
       </c>
@@ -959,7 +953,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>3</v>
       </c>
@@ -967,7 +961,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>4</v>
       </c>
@@ -975,23 +969,23 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" s="9">
         <v>0.1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B45" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>5</v>
       </c>
@@ -999,7 +993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
@@ -1007,7 +1001,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>7</v>
       </c>
@@ -1015,7 +1009,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>11</v>
       </c>
@@ -1023,7 +1017,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>12</v>
       </c>
@@ -1031,7 +1025,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>8</v>
       </c>
@@ -1039,7 +1033,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>11</v>
       </c>
@@ -1047,7 +1041,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>12</v>
       </c>
@@ -1055,7 +1049,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>13</v>
       </c>
@@ -1063,7 +1057,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>14</v>
       </c>
@@ -1071,7 +1065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>9</v>
       </c>
@@ -1079,15 +1073,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B57" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>15</v>
       </c>
@@ -1095,7 +1089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>10</v>
       </c>
@@ -1103,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>16</v>
       </c>
@@ -1111,7 +1105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>17</v>
       </c>
@@ -1119,20 +1113,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="19"/>
-      <c r="C62" s="20"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>1</v>
       </c>
@@ -1166,7 +1159,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B68" s="9">
         <v>0.05</v>
@@ -1174,7 +1167,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B69" s="9">
         <v>0.05</v>
@@ -1268,15 +1261,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B81" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>15</v>
       </c>
@@ -1284,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>10</v>
       </c>
@@ -1292,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>16</v>
       </c>
@@ -1300,7 +1293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>17</v>
       </c>
@@ -1308,20 +1301,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="18"/>
       <c r="B86" s="19"/>
-      <c r="C86" s="20"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>1</v>
       </c>
@@ -1329,7 +1321,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>2</v>
       </c>
@@ -1337,7 +1329,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>3</v>
       </c>
@@ -1345,7 +1337,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>4</v>
       </c>
@@ -1353,23 +1345,23 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B92" s="9">
         <v>0.1</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B93" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>5</v>
       </c>
@@ -1377,7 +1369,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>6</v>
       </c>
@@ -1385,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>7</v>
       </c>
@@ -1393,7 +1385,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>11</v>
       </c>
@@ -1401,7 +1393,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>12</v>
       </c>
@@ -1409,7 +1401,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>8</v>
       </c>
@@ -1417,7 +1409,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>11</v>
       </c>
@@ -1425,7 +1417,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>12</v>
       </c>
@@ -1433,7 +1425,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>13</v>
       </c>
@@ -1441,7 +1433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>14</v>
       </c>
@@ -1449,7 +1441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>9</v>
       </c>
@@ -1457,15 +1449,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B105" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>15</v>
       </c>
@@ -1473,7 +1465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>10</v>
       </c>
@@ -1481,7 +1473,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>16</v>
       </c>
@@ -1489,7 +1481,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>17</v>
       </c>
@@ -1497,21 +1489,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="18"/>
       <c r="B110" s="19"/>
-      <c r="C110" s="20"/>
-      <c r="D110" s="20"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B111" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>1</v>
       </c>
@@ -1545,7 +1535,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B116" s="9">
         <v>0.05</v>
@@ -1553,7 +1543,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B117" s="9">
         <v>0</v>
@@ -1647,15 +1637,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B129" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>15</v>
       </c>
@@ -1663,7 +1653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>10</v>
       </c>
@@ -1671,7 +1661,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>16</v>
       </c>
@@ -1679,7 +1669,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>17</v>
       </c>
@@ -1687,20 +1677,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
       <c r="B134" s="19"/>
-      <c r="C134" s="20"/>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>1</v>
       </c>
@@ -1708,7 +1697,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>2</v>
       </c>
@@ -1716,7 +1705,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>3</v>
       </c>
@@ -1724,7 +1713,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>4</v>
       </c>
@@ -1732,23 +1721,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B140" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B140" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="B141" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>5</v>
       </c>
@@ -1756,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>6</v>
       </c>
@@ -1764,7 +1753,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>7</v>
       </c>
@@ -1772,7 +1761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>11</v>
       </c>
@@ -1780,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>12</v>
       </c>
@@ -1788,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>8</v>
       </c>
@@ -1796,7 +1785,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>11</v>
       </c>
@@ -1804,7 +1793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>12</v>
       </c>
@@ -1812,7 +1801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>13</v>
       </c>
@@ -1820,7 +1809,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>14</v>
       </c>
@@ -1828,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>9</v>
       </c>
@@ -1836,15 +1825,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B153" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>15</v>
       </c>
@@ -1852,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>10</v>
       </c>
@@ -1860,7 +1849,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>16</v>
       </c>
@@ -1868,7 +1857,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>17</v>
       </c>
@@ -1876,21 +1865,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="18"/>
       <c r="B158" s="19"/>
-      <c r="C158" s="20"/>
-      <c r="D158" s="20"/>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B159" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>1</v>
       </c>
@@ -1924,7 +1911,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B164" s="9">
         <v>0.05</v>
@@ -1932,7 +1919,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B165" s="9">
         <v>0.05</v>
@@ -2026,15 +2013,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B177" s="12">
         <v>0.15</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>15</v>
       </c>
@@ -2042,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>10</v>
       </c>
@@ -2050,7 +2037,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>16</v>
       </c>
@@ -2058,7 +2045,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>17</v>
       </c>
@@ -2066,24 +2053,19 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="18"/>
       <c r="B182" s="19"/>
-      <c r="C182" s="20"/>
-      <c r="D182" s="20"/>
-      <c r="E182" s="20"/>
-      <c r="F182" s="20"/>
-      <c r="G182" s="20"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>1</v>
       </c>
@@ -2091,7 +2073,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>2</v>
       </c>
@@ -2099,7 +2081,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>3</v>
       </c>
@@ -2107,7 +2089,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>4</v>
       </c>
@@ -2115,23 +2097,23 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B188" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B188" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="B189" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>5</v>
       </c>
@@ -2139,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>6</v>
       </c>
@@ -2147,7 +2129,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>7</v>
       </c>
@@ -2155,7 +2137,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>11</v>
       </c>
@@ -2163,7 +2145,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
         <v>12</v>
       </c>
@@ -2171,7 +2153,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
         <v>8</v>
       </c>
@@ -2179,7 +2161,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
         <v>11</v>
       </c>
@@ -2187,7 +2169,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
         <v>12</v>
       </c>
@@ -2195,7 +2177,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
         <v>13</v>
       </c>
@@ -2203,7 +2185,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
         <v>14</v>
       </c>
@@ -2211,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>9</v>
       </c>
@@ -2219,15 +2201,15 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B201" s="12">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>15</v>
       </c>
@@ -2235,7 +2217,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>10</v>
       </c>
@@ -2243,7 +2225,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>16</v>
       </c>
@@ -2251,7 +2233,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>17</v>
       </c>
@@ -2259,21 +2241,19 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="18"/>
       <c r="B206" s="19"/>
-      <c r="C206" s="20"/>
-      <c r="D206" s="20"/>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>1</v>
       </c>
@@ -2307,7 +2287,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B212" s="9">
         <v>0</v>
@@ -2315,7 +2295,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B213" s="9">
         <v>0</v>
@@ -2411,7 +2391,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B225" s="12">
         <v>0.05</v>
@@ -2455,7 +2435,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B231" s="8" t="s">
         <v>0</v>
@@ -2495,7 +2475,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B236" s="9">
         <v>0</v>
@@ -2503,7 +2483,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B237" s="9">
         <v>0</v>
@@ -2599,7 +2579,7 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B249" s="12">
         <v>0.25</v>
@@ -2643,7 +2623,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B255" s="8" t="s">
         <v>0</v>
@@ -2683,7 +2663,7 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B260" s="9">
         <v>0</v>
@@ -2691,7 +2671,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B261" s="9">
         <v>0</v>
@@ -2787,7 +2767,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B273" s="12">
         <v>0.05</v>
@@ -2831,7 +2811,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B279" s="8" t="s">
         <v>0</v>
@@ -2871,7 +2851,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B284" s="9">
         <v>0</v>
@@ -2879,7 +2859,7 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B285" s="9">
         <v>0</v>
@@ -2975,7 +2955,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B297" s="12">
         <v>0.1</v>
